--- a/intake_forms/021_membership_crm_intake_form--intake_forms.xlsx
+++ b/intake_forms/021_membership_crm_intake_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'3-1',_'label':_'member',_'value':_'member'}</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '3-1', 'label': 'Member', 'value': 'Member'}</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'3-2',_'label':_'non-member',_'value':_'non-member'}</t>
+          <t>non-member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '3-2', 'label': 'Non-Member', 'value': 'Non-Member'}</t>
+          <t>Non-Member</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'4-1',_'label':_'payment_type_1',_'value':_'payment_type_1'}</t>
+          <t>payment_type_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '4-1', 'label': 'Payment Type 1', 'value': 'Payment Type 1'}</t>
+          <t>Payment Type 1</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'4-2',_'label':_'payment_type_2',_'value':_'payment_type_2'}</t>
+          <t>payment_type_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '4-2', 'label': 'Payment Type 2', 'value': 'Payment Type 2'}</t>
+          <t>Payment Type 2</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'7-1',_'label':_'payment_method_1',_'value':_'payment_method_1'}</t>
+          <t>payment_method_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '7-1', 'label': 'Payment Method 1', 'value': 'Payment Method 1'}</t>
+          <t>Payment Method 1</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'7-2',_'label':_'payment_method_2',_'value':_'payment_method_2'}</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '7-2', 'label': 'Payment Method 2', 'value': 'Payment Method 2'}</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'9-1',_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '9-1', 'label': 'Active', 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'9-2',_'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '9-2', 'label': 'inactive', 'value': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
